--- a/wyd_rate.xlsx
+++ b/wyd_rate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8080"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="rate" sheetId="6" r:id="rId1"/>
@@ -1333,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="7">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -1372,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="7">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="F3" s="7">
         <v>9</v>
@@ -1381,7 +1381,7 @@
         <v>10</v>
       </c>
       <c r="H3" s="7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -1573,7 +1573,7 @@
         <v>20</v>
       </c>
       <c r="H7" s="7">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -1618,10 +1618,10 @@
         <v>20</v>
       </c>
       <c r="G8" s="7">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="H8" s="7">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -1663,10 +1663,10 @@
         <v>22</v>
       </c>
       <c r="F9" s="7">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="G9" s="7">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="H9" s="7">
         <v>28</v>
@@ -1708,13 +1708,13 @@
         <v>24</v>
       </c>
       <c r="E10" s="7">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="F10" s="7">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="G10" s="7">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="H10" s="7">
         <v>30</v>
@@ -1756,13 +1756,13 @@
         <v>25</v>
       </c>
       <c r="E11" s="7">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="F11" s="7">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="G11" s="7">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="H11" s="7">
         <v>32</v>
@@ -1804,16 +1804,16 @@
         <v>27</v>
       </c>
       <c r="E12" s="7">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="F12" s="7">
         <v>29</v>
       </c>
       <c r="G12" s="7">
-        <v>31</v>
+        <v>31.25</v>
       </c>
       <c r="H12" s="7">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1858,10 +1858,10 @@
         <v>30</v>
       </c>
       <c r="G13" s="7">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="H13" s="7">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1900,7 +1900,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="7">
-        <v>31</v>
+        <v>31.25</v>
       </c>
       <c r="F14" s="7">
         <v>33</v>
@@ -1909,7 +1909,7 @@
         <v>35</v>
       </c>
       <c r="H14" s="7">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
